--- a/artfynd/A 36460-2026 artfynd.xlsx
+++ b/artfynd/A 36460-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347687</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36460-2026 artfynd.xlsx
+++ b/artfynd/A 36460-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347687</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36460-2026 artfynd.xlsx
+++ b/artfynd/A 36460-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347687</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
